--- a/Список товаров.xlsx
+++ b/Список товаров.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutoPrint V3.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BC3578-EDF2-4EBA-A47D-21FF0D5BA0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74347E6D-A8BF-4673-84F3-1D93735F5FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="4575" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1861,7 +1861,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>76</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>71</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>68</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>36</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>44</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>48</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>49</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>50</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>51</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>53</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
@@ -4100,7 +4100,7 @@
   <autoFilter ref="A1:M62" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="РУССКИЕ ЗАКУСКИ"/>
+        <filter val="Печагин"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
